--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486560_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486560_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.1711</v>
+        <v>5.177</v>
       </c>
       <c r="E2" t="n">
-        <v>5.6742</v>
+        <v>5.5876</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.5031</v>
+        <v>-0.4106</v>
       </c>
       <c r="G2" t="n">
         <v>4.2153</v>
@@ -610,13 +610,13 @@
         <v>1.0875</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.1318</v>
+        <v>-0.1259</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.1454</v>
+        <v>-0.2319</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0136</v>
+        <v>0.106</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.6165</v>
+        <v>4.2391</v>
       </c>
       <c r="E3" t="n">
-        <v>1.6795</v>
+        <v>2.487</v>
       </c>
       <c r="F3" t="n">
-        <v>1.937</v>
+        <v>1.752</v>
       </c>
       <c r="G3" t="n">
         <v>3.6839</v>
@@ -688,13 +688,13 @@
         <v>1.7401</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.1099</v>
+        <v>-0.4873</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.3699</v>
+        <v>-0.5624</v>
       </c>
       <c r="U3" t="n">
-        <v>0.26</v>
+        <v>0.0751</v>
       </c>
       <c r="V3" t="n">
         <v>1.695</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>G. RENFROE</t>
+          <t>J. KASIBABU SHILALA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,64 +721,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.9853</v>
+        <v>2.0031</v>
       </c>
       <c r="E4" t="n">
-        <v>1.6791</v>
+        <v>2.2149</v>
       </c>
       <c r="F4" t="n">
-        <v>0.3062</v>
+        <v>-0.2118</v>
       </c>
       <c r="G4" t="n">
-        <v>1.9113</v>
+        <v>1.9309</v>
       </c>
       <c r="H4" t="n">
-        <v>0.7574</v>
+        <v>1.6424</v>
       </c>
       <c r="I4" t="n">
-        <v>1.1538</v>
+        <v>0.2884</v>
       </c>
       <c r="J4" t="n">
-        <v>1.756</v>
+        <v>1.7421</v>
       </c>
       <c r="K4" t="n">
-        <v>0.6268</v>
+        <v>1.6274</v>
       </c>
       <c r="L4" t="n">
-        <v>1.1292</v>
+        <v>0.1147</v>
       </c>
       <c r="M4" t="n">
-        <v>0.1553</v>
+        <v>0.1888</v>
       </c>
       <c r="N4" t="n">
-        <v>0.1306</v>
+        <v>0.0151</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0247</v>
+        <v>0.1737</v>
       </c>
       <c r="P4" t="n">
-        <v>1.0875</v>
+        <v>0.87</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.2175</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.305</v>
+        <v>0.87</v>
       </c>
       <c r="S4" t="n">
-        <v>0.1164</v>
+        <v>0.137</v>
       </c>
       <c r="T4" t="n">
-        <v>0.1406</v>
+        <v>0.2776</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.0242</v>
+        <v>-0.1406</v>
       </c>
       <c r="V4" t="n">
-        <v>-1.13</v>
+        <v>-0.9347</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>0.1952</v>
       </c>
       <c r="X4" t="n">
         <v>-1.13</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. KASIBABU SHILALA</t>
+          <t>G. RENFROE</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.8114</v>
+        <v>1.9112</v>
       </c>
       <c r="E5" t="n">
-        <v>2.1464</v>
+        <v>1.6358</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.3351</v>
+        <v>0.2754</v>
       </c>
       <c r="G5" t="n">
-        <v>1.9309</v>
+        <v>1.9113</v>
       </c>
       <c r="H5" t="n">
-        <v>1.6424</v>
+        <v>0.7574</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2884</v>
+        <v>1.1538</v>
       </c>
       <c r="J5" t="n">
-        <v>1.7421</v>
+        <v>1.756</v>
       </c>
       <c r="K5" t="n">
-        <v>1.6274</v>
+        <v>0.6268</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1147</v>
+        <v>1.1292</v>
       </c>
       <c r="M5" t="n">
-        <v>0.1888</v>
+        <v>0.1553</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0151</v>
+        <v>0.1306</v>
       </c>
       <c r="O5" t="n">
-        <v>0.1737</v>
+        <v>0.0247</v>
       </c>
       <c r="P5" t="n">
-        <v>0.87</v>
+        <v>1.0875</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-0.2175</v>
       </c>
       <c r="R5" t="n">
-        <v>0.87</v>
+        <v>1.305</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.0548</v>
+        <v>0.0424</v>
       </c>
       <c r="T5" t="n">
-        <v>0.2091</v>
+        <v>0.0973</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.2639</v>
+        <v>-0.055</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.9347</v>
+        <v>-1.13</v>
       </c>
       <c r="W5" t="n">
-        <v>0.1952</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
         <v>-1.13</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.7477</v>
+        <v>0.4663</v>
       </c>
       <c r="E6" t="n">
-        <v>1.1384</v>
+        <v>0.5797</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.3908</v>
+        <v>-0.1134</v>
       </c>
       <c r="G6" t="n">
         <v>2.4325</v>
@@ -922,13 +922,13 @@
         <v>1.0875</v>
       </c>
       <c r="S6" t="n">
-        <v>0.1645</v>
+        <v>-0.1169</v>
       </c>
       <c r="T6" t="n">
-        <v>0.6682</v>
+        <v>0.1094</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.5036</v>
+        <v>-0.2262</v>
       </c>
       <c r="V6" t="n">
         <v>-0.5443</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.2729</v>
+        <v>-0.3962</v>
       </c>
       <c r="E8" t="n">
         <v>-0.1872</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.0857</v>
+        <v>-0.209</v>
       </c>
       <c r="G8" t="n">
         <v>-0.4647</v>
@@ -1078,13 +1078,13 @@
         <v>0.435</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.2432</v>
+        <v>-0.3665</v>
       </c>
       <c r="T8" t="n">
         <v>-0.2055</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.0377</v>
+        <v>-0.161</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.6241</v>
+        <v>-0.5933</v>
       </c>
       <c r="E9" t="n">
         <v>0.1188</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.7429</v>
+        <v>-0.7121</v>
       </c>
       <c r="G9" t="n">
         <v>0.4853</v>
@@ -1156,13 +1156,13 @@
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>0.0205</v>
+        <v>0.0514</v>
       </c>
       <c r="T9" t="n">
         <v>0.0805</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.06</v>
+        <v>-0.0291</v>
       </c>
       <c r="V9" t="n">
         <v>-1.13</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A. LIMA BRITO</t>
+          <t>M. DIAZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,64 +1189,64 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.5108</v>
+        <v>-1.5282</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.6794</v>
+        <v>-2.9989</v>
       </c>
       <c r="F10" t="n">
-        <v>0.1686</v>
+        <v>1.4707</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.9667</v>
+        <v>-2.2513</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.6209</v>
+        <v>1.1895</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.3459</v>
+        <v>-3.4408</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.863</v>
+        <v>-1.8727</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.9395</v>
+        <v>1.1259</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0765</v>
+        <v>-2.9985</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.1038</v>
+        <v>-0.3786</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.6814</v>
+        <v>0.0636</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.4224</v>
+        <v>-0.4423</v>
       </c>
       <c r="P10" t="n">
-        <v>1.305</v>
+        <v>-0.435</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-2.1751</v>
       </c>
       <c r="R10" t="n">
-        <v>1.305</v>
+        <v>1.7401</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.1096</v>
+        <v>-0.167</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.0769</v>
+        <v>-0.2764</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.0327</v>
+        <v>0.1093</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.7395</v>
+        <v>1.3252</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.7395</v>
+        <v>1.3252</v>
       </c>
       <c r="X10" t="n">
         <v>0</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>M. DIAZ</t>
+          <t>A. LIMA BRITO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,64 +1267,64 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.8973</v>
+        <v>-1.659</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.7379</v>
+        <v>-1.7659</v>
       </c>
       <c r="F11" t="n">
-        <v>1.8406</v>
+        <v>0.1069</v>
       </c>
       <c r="G11" t="n">
-        <v>-2.2513</v>
+        <v>-1.9667</v>
       </c>
       <c r="H11" t="n">
-        <v>1.1895</v>
+        <v>-1.6209</v>
       </c>
       <c r="I11" t="n">
-        <v>-3.4408</v>
+        <v>-0.3459</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.8727</v>
+        <v>-0.863</v>
       </c>
       <c r="K11" t="n">
-        <v>1.1259</v>
+        <v>-0.9395</v>
       </c>
       <c r="L11" t="n">
-        <v>-2.9985</v>
+        <v>0.0765</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.3786</v>
+        <v>-1.1038</v>
       </c>
       <c r="N11" t="n">
-        <v>0.0636</v>
+        <v>-0.6814</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.4423</v>
+        <v>-0.4224</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.435</v>
+        <v>1.305</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.1751</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.7401</v>
+        <v>1.305</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.5362</v>
+        <v>-0.2578</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.0154</v>
+        <v>-0.1634</v>
       </c>
       <c r="U11" t="n">
-        <v>0.4792</v>
+        <v>-0.09429999999999999</v>
       </c>
       <c r="V11" t="n">
-        <v>1.3252</v>
+        <v>-0.7395</v>
       </c>
       <c r="W11" t="n">
-        <v>1.3252</v>
+        <v>-0.7395</v>
       </c>
       <c r="X11" t="n">
         <v>0</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>J. BELEMENE-DZABATOU</t>
+          <t>D. MANCHON CRESPO</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1345,73 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.521</v>
+        <v>-2.104</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.8259</v>
+        <v>-0.8501</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.6951000000000001</v>
+        <v>-1.2538</v>
       </c>
       <c r="G12" t="n">
-        <v>-2.4838</v>
+        <v>-1.2741</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.9579</v>
+        <v>1.0248</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.526</v>
+        <v>-2.2989</v>
       </c>
       <c r="J12" t="n">
-        <v>-2.2766</v>
+        <v>-0.3815</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.9395</v>
+        <v>1.6242</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.3371</v>
+        <v>-2.0057</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.2073</v>
+        <v>-0.8925999999999999</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.0184</v>
+        <v>-0.5994</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.1889</v>
+        <v>-0.2933</v>
       </c>
       <c r="P12" t="n">
-        <v>0.87</v>
+        <v>1.0875</v>
       </c>
       <c r="Q12" t="n">
         <v>-0.2175</v>
       </c>
       <c r="R12" t="n">
-        <v>1.0875</v>
+        <v>1.305</v>
       </c>
       <c r="S12" t="n">
-        <v>0.6132</v>
+        <v>-0.7874</v>
       </c>
       <c r="T12" t="n">
-        <v>0.6682</v>
+        <v>-0.2511</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.0549</v>
+        <v>-0.5363</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.5204</v>
+        <v>-1.13</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.5204</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>D. MANCHON CRESPO</t>
+          <t>J. BELEMENE-DZABATOU</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-2.8169</v>
+        <v>-3.1424</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.4089</v>
+        <v>-2.5397</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.408</v>
+        <v>-0.6026</v>
       </c>
       <c r="G13" t="n">
-        <v>-1.2741</v>
+        <v>-2.4838</v>
       </c>
       <c r="H13" t="n">
-        <v>1.0248</v>
+        <v>-0.9579</v>
       </c>
       <c r="I13" t="n">
-        <v>-2.2989</v>
+        <v>-1.526</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.3815</v>
+        <v>-2.2766</v>
       </c>
       <c r="K13" t="n">
-        <v>1.6242</v>
+        <v>-0.9395</v>
       </c>
       <c r="L13" t="n">
-        <v>-2.0057</v>
+        <v>-1.3371</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.8925999999999999</v>
+        <v>-0.2073</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.5994</v>
+        <v>-0.0184</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.2933</v>
+        <v>-0.1889</v>
       </c>
       <c r="P13" t="n">
-        <v>1.0875</v>
+        <v>0.87</v>
       </c>
       <c r="Q13" t="n">
         <v>-0.2175</v>
       </c>
       <c r="R13" t="n">
-        <v>1.305</v>
+        <v>1.0875</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.5003</v>
+        <v>-0.0081</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.8099</v>
+        <v>-0.0457</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.6904</v>
+        <v>0.0375</v>
       </c>
       <c r="V13" t="n">
-        <v>-1.13</v>
+        <v>-1.5204</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>-1.13</v>
+        <v>-1.5204</v>
       </c>
     </row>
     <row r="14">
@@ -1501,22 +1501,22 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.689</v>
+        <v>4.373600000000001</v>
       </c>
       <c r="E14" t="n">
-        <v>3.597100000000001</v>
+        <v>4.281999999999999</v>
       </c>
       <c r="F14" t="n">
-        <v>0.09169999999999989</v>
+        <v>0.09169999999999967</v>
       </c>
       <c r="G14" t="n">
-        <v>6.3676</v>
+        <v>6.367599999999999</v>
       </c>
       <c r="H14" t="n">
-        <v>5.3991</v>
+        <v>5.399100000000001</v>
       </c>
       <c r="I14" t="n">
-        <v>0.9679999999999995</v>
+        <v>0.9679999999999993</v>
       </c>
       <c r="J14" t="n">
         <v>8.874499999999999</v>
@@ -1525,7 +1525,7 @@
         <v>5.918200000000001</v>
       </c>
       <c r="L14" t="n">
-        <v>2.956499999999999</v>
+        <v>2.9565</v>
       </c>
       <c r="M14" t="n">
         <v>-2.5071</v>
@@ -1546,19 +1546,19 @@
         <v>11.9627</v>
       </c>
       <c r="S14" t="n">
-        <v>-2.9202</v>
+        <v>-2.2351</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.8564</v>
+        <v>-1.1716</v>
       </c>
       <c r="U14" t="n">
         <v>-1.0636</v>
       </c>
       <c r="V14" t="n">
-        <v>-4.1087</v>
+        <v>-4.108699999999999</v>
       </c>
       <c r="W14" t="n">
-        <v>4.1916</v>
+        <v>4.191599999999999</v>
       </c>
       <c r="X14" t="n">
         <v>-8.3004</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.5732</v>
+        <v>6.044</v>
       </c>
       <c r="E15" t="n">
-        <v>5.2082</v>
+        <v>6.4375</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.635</v>
+        <v>-0.3935</v>
       </c>
       <c r="G15" t="n">
         <v>4.4126</v>
@@ -1624,13 +1624,13 @@
         <v>1.305</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.1869</v>
+        <v>0.2839</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.3014</v>
+        <v>-0.0721</v>
       </c>
       <c r="U15" t="n">
-        <v>0.1145</v>
+        <v>0.356</v>
       </c>
       <c r="V15" t="n">
         <v>1.13</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.025</v>
+        <v>3.3358</v>
       </c>
       <c r="E16" t="n">
-        <v>2.5323</v>
+        <v>2.7558</v>
       </c>
       <c r="F16" t="n">
-        <v>0.4927</v>
+        <v>0.58</v>
       </c>
       <c r="G16" t="n">
         <v>1.6882</v>
@@ -1702,13 +1702,13 @@
         <v>1.0875</v>
       </c>
       <c r="S16" t="n">
-        <v>0.1644</v>
+        <v>0.4753</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.1454</v>
+        <v>0.0781</v>
       </c>
       <c r="U16" t="n">
-        <v>0.3098</v>
+        <v>0.3972</v>
       </c>
       <c r="V16" t="n">
         <v>2.2599</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.885</v>
+        <v>1.6814</v>
       </c>
       <c r="E17" t="n">
-        <v>2.0333</v>
+        <v>0.8038999999999999</v>
       </c>
       <c r="F17" t="n">
-        <v>0.8517</v>
+        <v>0.8774999999999999</v>
       </c>
       <c r="G17" t="n">
         <v>1.5594</v>
@@ -1780,13 +1780,13 @@
         <v>0.87</v>
       </c>
       <c r="S17" t="n">
-        <v>1.7384</v>
+        <v>0.5348000000000001</v>
       </c>
       <c r="T17" t="n">
-        <v>1.6872</v>
+        <v>0.4579</v>
       </c>
       <c r="U17" t="n">
-        <v>0.0512</v>
+        <v>0.0769</v>
       </c>
       <c r="V17" t="n">
         <v>-0.1952</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>2.6032</v>
+        <v>1.3315</v>
       </c>
       <c r="E18" t="n">
-        <v>3.9926</v>
+        <v>2.875</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.3894</v>
+        <v>-1.5435</v>
       </c>
       <c r="G18" t="n">
         <v>1.236</v>
@@ -1858,13 +1858,13 @@
         <v>0.435</v>
       </c>
       <c r="S18" t="n">
-        <v>2.2574</v>
+        <v>0.9857</v>
       </c>
       <c r="T18" t="n">
-        <v>1.8242</v>
+        <v>0.7066</v>
       </c>
       <c r="U18" t="n">
-        <v>0.4332</v>
+        <v>0.2791</v>
       </c>
       <c r="V18" t="n">
         <v>-1.3252</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. GONZÁLEZ PÉREZ</t>
+          <t>S. SALIN</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.3125</v>
+        <v>-0.4278</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.243</v>
+        <v>-1.4153</v>
       </c>
       <c r="F19" t="n">
-        <v>0.9305</v>
+        <v>0.9874000000000001</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.6004</v>
+        <v>-2.6111</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.1254</v>
+        <v>-1.6485</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.4749</v>
+        <v>-0.9626</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.6321</v>
+        <v>-2.2388</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.7086</v>
+        <v>-1.3806</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0765</v>
+        <v>-0.8582</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.9683</v>
+        <v>-0.3723</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.4169</v>
+        <v>-0.2679</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.5514</v>
+        <v>-0.1044</v>
       </c>
       <c r="P19" t="n">
-        <v>0.2175</v>
+        <v>0.87</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>0.2175</v>
+        <v>0.87</v>
       </c>
       <c r="S19" t="n">
-        <v>1.0703</v>
+        <v>0.1833</v>
       </c>
       <c r="T19" t="n">
-        <v>0.1286</v>
+        <v>-0.3064</v>
       </c>
       <c r="U19" t="n">
-        <v>0.9418</v>
+        <v>0.4897</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="W19" t="n">
-        <v>-0.7395</v>
+        <v>1.13</v>
       </c>
       <c r="X19" t="n">
-        <v>0.7395</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>S. SALIN</t>
+          <t>A. GONZÁLEZ PÉREZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.0598</v>
+        <v>-0.9367</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.8623</v>
+        <v>-1.4665</v>
       </c>
       <c r="F20" t="n">
-        <v>0.8025</v>
+        <v>0.5298</v>
       </c>
       <c r="G20" t="n">
-        <v>-2.6111</v>
+        <v>-1.6004</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.6485</v>
+        <v>-1.1254</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.9626</v>
+        <v>-0.4749</v>
       </c>
       <c r="J20" t="n">
-        <v>-2.2388</v>
+        <v>-0.6321</v>
       </c>
       <c r="K20" t="n">
-        <v>-1.3806</v>
+        <v>-0.7086</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.8582</v>
+        <v>0.0765</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.3723</v>
+        <v>-0.9683</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.2679</v>
+        <v>-0.4169</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.1044</v>
+        <v>-0.5514</v>
       </c>
       <c r="P20" t="n">
-        <v>0.87</v>
+        <v>0.2175</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0.87</v>
+        <v>0.2175</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.4487</v>
+        <v>0.4461</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.7534999999999999</v>
+        <v>-0.0949</v>
       </c>
       <c r="U20" t="n">
-        <v>0.3047</v>
+        <v>0.5411</v>
       </c>
       <c r="V20" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>1.13</v>
+        <v>-0.7395</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>0.7395</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>T. MC GREW</t>
+          <t>R. STUMBRIS</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.5621</v>
+        <v>-1.0517</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.145</v>
+        <v>0.1178</v>
       </c>
       <c r="F21" t="n">
-        <v>0.5829</v>
+        <v>-1.1695</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.0828</v>
+        <v>-2.4588</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.1217</v>
+        <v>-1.6332</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.9611</v>
+        <v>-0.8255</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.7256</v>
+        <v>-1.041</v>
       </c>
       <c r="K21" t="n">
-        <v>0.2801</v>
+        <v>-0.8514</v>
       </c>
       <c r="L21" t="n">
-        <v>-2.0057</v>
+        <v>-0.1896</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.3572</v>
+        <v>-1.4178</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.4018</v>
+        <v>-0.7819</v>
       </c>
       <c r="O21" t="n">
-        <v>0.0446</v>
+        <v>-0.6359</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.435</v>
+        <v>0.87</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.0875</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>0.6525</v>
+        <v>0.87</v>
       </c>
       <c r="S21" t="n">
-        <v>0.9557</v>
+        <v>-0.2025</v>
       </c>
       <c r="T21" t="n">
-        <v>0.6682</v>
+        <v>0.0288</v>
       </c>
       <c r="U21" t="n">
-        <v>0.2876</v>
+        <v>-0.2313</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>0.7395</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-0.3904</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>R. STUMBRIS</t>
+          <t>T. MC GREW</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.1422</v>
+        <v>-1.8794</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.6645</v>
+        <v>-2.7038</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.4778</v>
+        <v>0.8244</v>
       </c>
       <c r="G22" t="n">
-        <v>-2.4588</v>
+        <v>-2.0828</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.6332</v>
+        <v>-0.1217</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.8255</v>
+        <v>-1.9611</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.041</v>
+        <v>-1.7256</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.8514</v>
+        <v>0.2801</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.1896</v>
+        <v>-2.0057</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.4178</v>
+        <v>-0.3572</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.7819</v>
+        <v>-0.4018</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.6359</v>
+        <v>0.0446</v>
       </c>
       <c r="P22" t="n">
-        <v>0.87</v>
+        <v>-0.435</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>-1.0875</v>
       </c>
       <c r="R22" t="n">
-        <v>0.87</v>
+        <v>0.6525</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.293</v>
+        <v>0.6384</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.7534999999999999</v>
+        <v>0.1094</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.5396</v>
+        <v>0.529</v>
       </c>
       <c r="V22" t="n">
-        <v>0.7395</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.3904</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.6984</v>
+        <v>-2.2899</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.2103</v>
+        <v>-0.9868</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.4881</v>
+        <v>-1.3031</v>
       </c>
       <c r="G23" t="n">
         <v>-0.2186</v>
@@ -2248,13 +2248,13 @@
         <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.8272</v>
+        <v>-0.4188</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.274</v>
+        <v>-0.0505</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.5533</v>
+        <v>-0.3683</v>
       </c>
       <c r="V23" t="n">
         <v>-0.5649999999999999</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.004</v>
+        <v>-2.3463</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.1134</v>
+        <v>-1.6664</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.8905999999999999</v>
+        <v>-0.6798999999999999</v>
       </c>
       <c r="G24" t="n">
         <v>-1.7825</v>
@@ -2326,13 +2326,13 @@
         <v>1.0875</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.1764</v>
+        <v>0.4813</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.4194</v>
+        <v>0.0277</v>
       </c>
       <c r="U24" t="n">
-        <v>0.243</v>
+        <v>0.4536</v>
       </c>
       <c r="V24" t="n">
         <v>1.13</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-5.9962</v>
+        <v>-6.4046</v>
       </c>
       <c r="E25" t="n">
-        <v>-4.6197</v>
+        <v>-4.8432</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.3764</v>
+        <v>-1.5614</v>
       </c>
       <c r="G25" t="n">
         <v>-4.5096</v>
@@ -2404,13 +2404,13 @@
         <v>0.2175</v>
       </c>
       <c r="S25" t="n">
-        <v>0.6662</v>
+        <v>0.2578</v>
       </c>
       <c r="T25" t="n">
-        <v>0.4026</v>
+        <v>0.1791</v>
       </c>
       <c r="U25" t="n">
-        <v>0.2636</v>
+        <v>0.07870000000000001</v>
       </c>
       <c r="V25" t="n">
         <v>-0.1952</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-3.688799999999997</v>
+        <v>-2.9437</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.09179999999999922</v>
+        <v>-0.09199999999999964</v>
       </c>
       <c r="F26" t="n">
-        <v>-3.597</v>
+        <v>-2.8518</v>
       </c>
       <c r="G26" t="n">
         <v>-6.367599999999999</v>
@@ -2482,13 +2482,13 @@
         <v>7.6125</v>
       </c>
       <c r="S26" t="n">
-        <v>2.9202</v>
+        <v>3.6653</v>
       </c>
       <c r="T26" t="n">
-        <v>1.063600000000001</v>
+        <v>1.0637</v>
       </c>
       <c r="U26" t="n">
-        <v>1.8565</v>
+        <v>2.601700000000001</v>
       </c>
       <c r="V26" t="n">
         <v>4.1088</v>
